--- a/healthcare_surveys/038_healthcare_funding_quiz--healthcare_surveys.xlsx
+++ b/healthcare_surveys/038_healthcare_funding_quiz--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -746,8 +746,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,12 +775,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'cost_and_insurance_coverage'}</t>
+          <t>cost_and_insurance_coverage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Cost and insurance coverage'}</t>
+          <t>Cost and insurance coverage</t>
         </is>
       </c>
     </row>
@@ -792,12 +792,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'affordability'}</t>
+          <t>affordability</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Affordability'}</t>
+          <t>Affordability</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'private_insurance'}</t>
+          <t>private_insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Private insurance'}</t>
+          <t>Private insurance</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'medicaid'}</t>
+          <t>medicaid</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Medicaid'}</t>
+          <t>Medicaid</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'medicare'}</t>
+          <t>medicare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Medicare'}</t>
+          <t>Medicare</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'self-pay'}</t>
+          <t>self-pay</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Self-pay'}</t>
+          <t>Self-pay</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Phone call'}</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
